--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63838.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63838.xlsx
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S1-01-G1</t>
+          <t>51-01-G1</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name nom</t>
+          <t>Knn</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,11 @@
           <t>Nom</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -578,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G00A</t>
+          <t>G01B</t>
         </is>
       </c>
     </row>
@@ -589,7 +593,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52727</v>
+        <v>63838</v>
       </c>
     </row>
     <row r="18">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63838.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63838.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G01B</t>
+          <t>G01H</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63838.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63838.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Knn</t>
+          <t>Rnn</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>EL</t>
         </is>
       </c>
     </row>
@@ -727,10 +727,10 @@
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>2.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63838.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63838.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rnn</t>
+          <t>RNN</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_63838.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_63838.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
